--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_o_higgins.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:30</t>
+    <t xml:space="preserve">2026-09-24 01:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -733,13 +733,13 @@
         <v>-0.33</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.53</v>
@@ -753,19 +753,19 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="12">
@@ -779,13 +779,13 @@
         <v>-0.44</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.6</v>
@@ -799,16 +799,16 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.6</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_o_higgins.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:20</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_o_higgins.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
